--- a/output/pdf_financials_xlsx/FTJ.xlsx
+++ b/output/pdf_financials_xlsx/FTJ.xlsx
@@ -5969,13 +5969,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.432043</v>
+        <v>2.106244</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.432043</v>
+        <v>1.491988</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.432043</v>
+        <v>1.722805</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -5988,19 +5988,19 @@
         </is>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.432043</v>
+        <v>0.77454</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.432043</v>
+        <v>0.647776</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.432043</v>
+        <v>0.890639</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.432043</v>
+        <v>0.761357</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.432043</v>
+        <v>0.588124</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0.432043</v>
@@ -12504,7 +12504,11 @@
           <t>Share Purchase Warrants Reserve</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -17580,7 +17584,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -17674,7 +17682,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -19302,7 +19314,11 @@
           <t>Share-based payment reserve (Notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.126</v>
       </c>
@@ -19394,7 +19410,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E116" s="5" t="n">
         <v>1.548201</v>
       </c>

--- a/output/pdf_financials_xlsx/FTJ.xlsx
+++ b/output/pdf_financials_xlsx/FTJ.xlsx
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2.5e-05</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>5.086769</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.713817</v>
+        <v>-0.713842</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>5.086769</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.711865</v>
+        <v>-0.71189</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2460,37 +2460,37 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007535</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004472</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009701</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001877</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.004733</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.001483</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.000322</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>2.3e-05</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
     </row>
     <row r="35">
@@ -2578,37 +2578,37 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007535</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000304</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004472</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009701</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001877</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.004733</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.001483</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000743</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.000322</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>2.3e-05</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
     </row>
     <row r="37">
@@ -3286,37 +3286,37 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.007535</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004472</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009701</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.001877</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.004733</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.001483</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.000743</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.000322</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.3e-05</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -36202,7 +36202,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -36872,7 +36872,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -38036,7 +38036,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -49542,7 +49542,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
